--- a/output/full_scan/batch_seq7_2026-09-15.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-15.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6491</v>
+        <v>6538</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>684.7156829619081</v>
+        <v>729.85486994922</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.51126958760049</v>
+        <v>81.99933188316078</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.46541670327057</v>
+        <v>58.71718992211328</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.52449476163908</v>
+        <v>0.0729412341115082</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-1.187143516563838</v>
+        <v>10.54357434739281</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6560</v>
+        <v>6491</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>663.2593479339322</v>
+        <v>684.7156829619081</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31.85</v>
+        <v>390</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>52.32368651671867</v>
+        <v>59.51126958760049</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10.2223230747557</v>
+        <v>23.46541670327057</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.496555136842907</v>
+        <v>1.52449476163908</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3256705083064126</v>
+        <v>-1.187143516563838</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6672</v>
+        <v>6560</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>656.9556647721247</v>
+        <v>663.2593479339322</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>291</v>
+        <v>31.85</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.60572291968151</v>
+        <v>52.32368651671867</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>21.09526628931243</v>
+        <v>10.2223230747557</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.8704579020218109</v>
+        <v>5.496555136842907</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.0537740992613837</v>
+        <v>0.3256705083064126</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6706</v>
+        <v>6672</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>656.2839688874219</v>
+        <v>656.9556647721247</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>143.5</v>
+        <v>291</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.92268589762205</v>
+        <v>56.60572291968151</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.36896581071804</v>
+        <v>21.09526628931243</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.074586921976024</v>
+        <v>0.8704579020218109</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.635338796205758</v>
+        <v>-0.0537740992613837</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6510</v>
+        <v>6706</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>647.9864588471385</v>
+        <v>656.2839688874219</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3255</v>
+        <v>143.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.0990345757299</v>
+        <v>63.92268589762205</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.86625993002571</v>
+        <v>26.36896581071804</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.874651760709606</v>
+        <v>5.074586921976024</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>20.45888481179165</v>
+        <v>2.635338796205758</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6716</v>
+        <v>6510</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>619.3402645421478</v>
+        <v>647.9864588471385</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>115</v>
+        <v>3255</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>47.91184986495243</v>
+        <v>54.0990345757299</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.93639879294361</v>
+        <v>33.86625993002571</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7192140654347325</v>
+        <v>0.874651760709606</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-2.29550246406785</v>
+        <v>20.45888481179165</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6655</v>
+        <v>6716</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>616.3992307782783</v>
+        <v>619.3402645421478</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>53.17640120689472</v>
+        <v>47.91184986495243</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11.89456099852568</v>
+        <v>27.93639879294361</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.739923077827831</v>
+        <v>0.7192140654347325</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.569425908278432</v>
+        <v>-2.29550246406785</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6532</v>
+        <v>6655</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>616.0267821217246</v>
+        <v>616.3992307782783</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>91.7</v>
+        <v>123</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.31679824520216</v>
+        <v>53.17640120689472</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.47952605028858</v>
+        <v>11.89456099852568</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3571443135878606</v>
+        <v>1.739923077827831</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.8967382842938516</v>
+        <v>2.569425908278432</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6668</v>
+        <v>6532</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>604.1687611388562</v>
+        <v>616.0267821217246</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42.7</v>
+        <v>91.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.60527580700348</v>
+        <v>51.31679824520216</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.15147407610772</v>
+        <v>39.47952605028858</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.247194296616126</v>
+        <v>0.3571443135878606</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.08791141174676601</v>
+        <v>-0.8967382842938516</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6715</v>
+        <v>6668</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>595.6535790687609</v>
+        <v>604.1687611388562</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>357.5</v>
+        <v>42.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.95847042885099</v>
+        <v>58.60527580700348</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10.5316737674188</v>
+        <v>36.15147407610772</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.802128231076225</v>
+        <v>2.247194296616126</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.499181528271706</v>
+        <v>-0.08791141174676601</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6505</v>
+        <v>6715</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>595.3586138998894</v>
+        <v>595.6535790687609</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>357.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.00381006996444</v>
+        <v>49.95847042885099</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>38.64636434589529</v>
+        <v>10.5316737674188</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.690724461201233</v>
+        <v>1.802128231076225</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.6468972776802793</v>
+        <v>1.499181528271706</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6683</v>
+        <v>6505</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>585.1177252786707</v>
+        <v>595.3586138998894</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1450</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.60236375575815</v>
+        <v>61.00381006996444</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13.55479509522968</v>
+        <v>38.64636434589529</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.325299747628601</v>
+        <v>0.690724461201233</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>12.79111641253786</v>
+        <v>0.6468972776802793</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6530</v>
+        <v>6683</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>554.2481099511297</v>
+        <v>585.1177252786707</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>89.5</v>
+        <v>1450</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>50.34027301342034</v>
+        <v>59.60236375575815</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.50249861660388</v>
+        <v>13.55479509522968</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4401903326688893</v>
+        <v>2.325299747628601</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.625988223383481</v>
+        <v>12.79111641253786</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6654</v>
+        <v>6530</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>550.2057173717717</v>
+        <v>554.2481099511297</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>199</v>
+        <v>89.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.21200512773894</v>
+        <v>50.34027301342034</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.22734235625896</v>
+        <v>27.50249861660388</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2548088511417039</v>
+        <v>0.4401903326688893</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.008115928972919999</v>
+        <v>-0.625988223383481</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6782</v>
+        <v>6654</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>547.5152106626614</v>
+        <v>550.2057173717717</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.59372432964911</v>
+        <v>54.21200512773894</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.61408487599416</v>
+        <v>26.22734235625896</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3106777985096403</v>
+        <v>0.2548088511417039</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.125379315426352</v>
+        <v>-0.008115928972919999</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6830</v>
+        <v>6782</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>534.4402491219735</v>
+        <v>547.5152106626614</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>532</v>
+        <v>231</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.97095454205538</v>
+        <v>55.59372432964911</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.59690679849987</v>
+        <v>22.61408487599416</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3710705696293394</v>
+        <v>0.3106777985096403</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,48 +1471,48 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-4.644521158753307</v>
+        <v>-2.125379315426352</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6806</v>
+        <v>6830</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>534.4402491219735</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3.51</v>
+        <v>532</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>31.69502451113186</v>
+        <v>52.97095454205538</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.59322678573952</v>
+        <v>34.59690679849987</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.3710705696293394</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,48 +1524,48 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.4112821176437218</v>
+        <v>-4.644521158753307</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6691</v>
+        <v>6806</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>500.3403608834523</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>608</v>
+        <v>3.51</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>39.76936836158019</v>
+        <v>31.69502451113186</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.80021064230384</v>
+        <v>32.59322678573952</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.3851850093417134</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.65144092973393</v>
+        <v>0.4112821176437218</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6613</v>
+        <v>6691</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>498.7424636762564</v>
+        <v>500.3403608834523</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>255</v>
+        <v>608</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>42.24313576346995</v>
+        <v>39.76936836158019</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8.561488028655095</v>
+        <v>20.80021064230384</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3980935593947328</v>
+        <v>0.3851850093417134</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.8032139946985426</v>
+        <v>1.65144092973393</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6657</v>
+        <v>6613</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>478.3510934586142</v>
+        <v>498.7424636762564</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>33.6</v>
+        <v>255</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.12937671247724</v>
+        <v>42.24313576346995</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25.69068827604676</v>
+        <v>8.561488028655095</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7849967092881418</v>
+        <v>0.3980935593947328</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5330154741992911</v>
+        <v>0.8032139946985426</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6805</v>
+        <v>6657</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>476.6372682027734</v>
+        <v>478.3510934586142</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2025</v>
+        <v>33.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.17989954396081</v>
+        <v>55.12937671247724</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.93959722967056</v>
+        <v>25.69068827604676</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7889729977733463</v>
+        <v>0.7849967092881418</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-27.64344975401994</v>
+        <v>0.5330154741992911</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6667</v>
+        <v>6805</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>459.4787142836582</v>
+        <v>476.6372682027734</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>236</v>
+        <v>2025</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.84794974231231</v>
+        <v>50.17989954396081</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.40092805563898</v>
+        <v>26.93959722967056</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6707002442326818</v>
+        <v>0.7889729977733463</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.32692964001569</v>
+        <v>-27.64344975401994</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6670</v>
+        <v>6667</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>454.0413348994078</v>
+        <v>459.4787142836582</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>270.5</v>
+        <v>236</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.40041151215228</v>
+        <v>50.84794974231231</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.46876807721394</v>
+        <v>33.40092805563898</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7796263917235956</v>
+        <v>0.6707002442326818</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.7553129294795822</v>
+        <v>2.32692964001569</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6651</v>
+        <v>6670</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>453.7439371333308</v>
+        <v>454.0413348994078</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>141.5</v>
+        <v>270.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.73285384547426</v>
+        <v>48.40041151215228</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.80557455195759</v>
+        <v>29.46876807721394</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2105210679801834</v>
+        <v>0.7796263917235956</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.437422403316028</v>
+        <v>-0.7553129294795822</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6829</v>
+        <v>6651</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>453.7158407692006</v>
+        <v>453.7439371333308</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>204</v>
+        <v>141.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>41.46216296822757</v>
+        <v>49.73285384547426</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.09615457387502</v>
+        <v>21.80557455195759</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.089874190632301</v>
+        <v>0.2105210679801834</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-4.579309378958691</v>
+        <v>-1.437422403316028</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6588</v>
+        <v>6829</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>446.9939178316373</v>
+        <v>453.7158407692006</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45.65298731791779</v>
+        <v>41.46216296822757</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.27093953260516</v>
+        <v>19.09615457387502</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3363140524360854</v>
+        <v>1.089874190632301</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.433893667389062</v>
+        <v>-4.579309378958691</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6834</v>
+        <v>6588</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>446.1332358772327</v>
+        <v>446.9939178316373</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.5753433675246</v>
+        <v>45.65298731791779</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.70073407449943</v>
+        <v>26.27093953260516</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.20408230980904</v>
+        <v>0.3363140524360854</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.9719769739327956</v>
+        <v>-1.433893667389062</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6727</v>
+        <v>6834</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>445.010311591672</v>
+        <v>446.1332358772327</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>469.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.53662156242728</v>
+        <v>50.5753433675246</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.30049882399678</v>
+        <v>17.70073407449943</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6297906288307152</v>
+        <v>1.20408230980904</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-9.784371160289997</v>
+        <v>0.9719769739327956</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6640</v>
+        <v>6727</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>436.7074954440278</v>
+        <v>445.010311591672</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1100</v>
+        <v>469.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.54580344359461</v>
+        <v>46.53662156242728</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.15550718099339</v>
+        <v>24.30049882399678</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.334554345701705</v>
+        <v>0.6297906288307152</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-7.697622985369243</v>
+        <v>-9.784371160289997</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6548</v>
+        <v>6640</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>435.063764002308</v>
+        <v>436.7074954440278</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>71.7</v>
+        <v>1100</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.60559167286016</v>
+        <v>49.54580344359461</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>9.987392211013294</v>
+        <v>27.15550718099339</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6637793158864846</v>
+        <v>0.334554345701705</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0497152283112318</v>
+        <v>-7.697622985369243</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6666</v>
+        <v>6548</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>434.3185186390002</v>
+        <v>435.063764002308</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44</v>
+        <v>71.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.83303655108319</v>
+        <v>48.60559167286016</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.95216050851909</v>
+        <v>9.987392211013294</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9408937037509848</v>
+        <v>0.6637793158864846</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.044926356700685</v>
+        <v>-0.0497152283112318</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6693</v>
+        <v>6666</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>411.6409557524584</v>
+        <v>434.3185186390002</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>173.5</v>
+        <v>44</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.46782268650077</v>
+        <v>48.83303655108319</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.19222404165153</v>
+        <v>12.95216050851909</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6573488774005452</v>
+        <v>0.9408937037509848</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2426295614437819</v>
+        <v>-0.044926356700685</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6689</v>
+        <v>6693</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>411</v>
+        <v>411.6409557524584</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.3</v>
+        <v>173.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>66.94821733476414</v>
+        <v>47.46782268650077</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.64326101564129</v>
+        <v>14.19222404165153</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12.07228937583541</v>
+        <v>0.6573488774005452</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.8770061884136047</v>
+        <v>0.2426295614437819</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6581</v>
+        <v>6689</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>405.912101181866</v>
+        <v>411</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>109</v>
+        <v>69.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.49019604060943</v>
+        <v>66.94821733476414</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25.11002670660743</v>
+        <v>17.64326101564129</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.747069632797956</v>
+        <v>12.07228937583541</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.07260044077167931</v>
+        <v>0.8770061884136047</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6486</v>
+        <v>6581</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>401.1300479547394</v>
+        <v>405.912101181866</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.87396590825599</v>
+        <v>48.49019604060943</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>42.39741742781498</v>
+        <v>25.11002670660743</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2425194360715431</v>
+        <v>1.747069632797956</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0849198467619363</v>
+        <v>0.07260044077167931</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6584</v>
+        <v>6486</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>394.4724371973074</v>
+        <v>401.1300479547394</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>537</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>39.98951055200581</v>
+        <v>53.87396590825599</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.96006812142448</v>
+        <v>42.39741742781498</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1941835916150109</v>
+        <v>0.2425194360715431</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-12.05948284404052</v>
+        <v>0.0849198467619363</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6770</v>
+        <v>6584</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>377.1547883040272</v>
+        <v>394.4724371973074</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>537</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>44.48170093679794</v>
+        <v>39.98951055200581</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.957281093064282</v>
+        <v>21.96006812142448</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.148703237207513</v>
+        <v>0.1941835916150109</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.3366429946684313</v>
+        <v>-12.05948284404052</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6605</v>
+        <v>6770</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>375.2026626642516</v>
+        <v>377.1547883040272</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>137.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.72376418922047</v>
+        <v>44.48170093679794</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11.5125463343296</v>
+        <v>9.957281093064282</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.060091392175252</v>
+        <v>1.148703237207513</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.3271169002981708</v>
+        <v>-0.3366429946684313</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6579</v>
+        <v>6605</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>374.1172718454847</v>
+        <v>375.2026626642516</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>147.5</v>
+        <v>137.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.81709058705352</v>
+        <v>50.72376418922047</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.82332086141</v>
+        <v>11.5125463343296</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7083905639301286</v>
+        <v>1.060091392175252</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.545793558085649</v>
+        <v>-0.3271169002981708</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6642</v>
+        <v>6579</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>370.5182675931749</v>
+        <v>374.1172718454847</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>147.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.62294949712422</v>
+        <v>44.81709058705352</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.40376252252222</v>
+        <v>20.82332086141</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2756515675215171</v>
+        <v>0.7083905639301286</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.6600529416256458</v>
+        <v>0.545793558085649</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6768</v>
+        <v>6642</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>369.6766809362481</v>
+        <v>370.5182675931749</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>62.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>34.46676255508363</v>
+        <v>41.62294949712422</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.55834774604533</v>
+        <v>14.40376252252222</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6692028291916149</v>
+        <v>0.2756515675215171</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0084387674855685</v>
+        <v>-0.6600529416256458</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6708</v>
+        <v>6768</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>365.4145558845698</v>
+        <v>369.6766809362481</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>37.35</v>
+        <v>62.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.76665355683206</v>
+        <v>34.46676255508363</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5.845313891646164</v>
+        <v>30.55834774604533</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.845929910608338</v>
+        <v>0.6692028291916149</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3134469314971608</v>
+        <v>0.0084387674855685</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6742</v>
+        <v>6708</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>362.8893705425612</v>
+        <v>365.4145558845698</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>44.2</v>
+        <v>37.35</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.30733971507549</v>
+        <v>50.76665355683206</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.79803744073117</v>
+        <v>5.845313891646164</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5809791699874319</v>
+        <v>1.845929910608338</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2384970576252891</v>
+        <v>-0.3134469314971608</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6664</v>
+        <v>6742</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>361.214962887356</v>
+        <v>362.8893705425612</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>333</v>
+        <v>44.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.64484840999605</v>
+        <v>46.30733971507549</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.8466631895234</v>
+        <v>24.79803744073117</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2254550134016023</v>
+        <v>0.5809791699874319</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.25672081623633</v>
+        <v>0.2384970576252891</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6669</v>
+        <v>6664</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>360.1853486166084</v>
+        <v>361.214962887356</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>26.49571003043009</v>
+        <v>40.64484840999605</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>41.02588244931377</v>
+        <v>11.8466631895234</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9113751118601972</v>
+        <v>0.2254550134016023</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-293.8647104568006</v>
+        <v>-2.25672081623633</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6789</v>
+        <v>6669</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>353.9081247172306</v>
+        <v>360.1853486166084</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>425</v>
+        <v>2315</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.02871138496766</v>
+        <v>26.49571003043009</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.66156932789742</v>
+        <v>41.02588244931377</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4989593848420265</v>
+        <v>0.9113751118601972</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-3.041336244230958</v>
+        <v>-293.8647104568006</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6684</v>
+        <v>6789</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>351.7467815100449</v>
+        <v>353.9081247172306</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>44.4</v>
+        <v>425</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>37.17539806020054</v>
+        <v>40.02871138496766</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7.735847938012192</v>
+        <v>14.66156932789742</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7091177810770775</v>
+        <v>0.4989593848420265</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0925769559764783</v>
+        <v>-3.041336244230958</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6719</v>
+        <v>6684</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>347.3648638216309</v>
+        <v>351.7467815100449</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>179</v>
+        <v>44.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>34.53097128530672</v>
+        <v>37.17539806020054</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.61652923035223</v>
+        <v>7.735847938012192</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5155366509914783</v>
+        <v>0.7091177810770775</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2661653131800925</v>
+        <v>-0.0925769559764783</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6690</v>
+        <v>6719</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>344</v>
+        <v>347.3648638216309</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>183.5</v>
+        <v>179</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>71.53167701435646</v>
+        <v>34.53097128530672</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.13767848497219</v>
+        <v>25.61652923035223</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>12.02116237519267</v>
+        <v>0.5155366509914783</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.297460292033472</v>
+        <v>0.2661653131800925</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6658</v>
+        <v>6690</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>340.8093055770312</v>
+        <v>344</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>163</v>
+        <v>183.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.89674587116541</v>
+        <v>71.53167701435646</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.62159287055706</v>
+        <v>19.13767848497219</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2881869758336829</v>
+        <v>12.02116237519267</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.038273917080957</v>
+        <v>2.297460292033472</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6771</v>
+        <v>6658</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>340.4183524181706</v>
+        <v>340.8093055770312</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>41.7</v>
+        <v>163</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.40563194480311</v>
+        <v>45.89674587116541</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.00245101266772</v>
+        <v>14.62159287055706</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6762267879631586</v>
+        <v>0.2881869758336829</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1265335105756108</v>
+        <v>-1.038273917080957</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6515</v>
+        <v>6771</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>336.8316871436749</v>
+        <v>340.4183524181706</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>6310</v>
+        <v>41.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.39126811181405</v>
+        <v>55.40563194480311</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.79510086497888</v>
+        <v>24.00245101266772</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7157423507806016</v>
+        <v>0.6762267879631586</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-8.947872376930704</v>
+        <v>-0.1265335105756108</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6585</v>
+        <v>6515</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>333.2175191820899</v>
+        <v>336.8316871436749</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.5</v>
+        <v>6310</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>31.34088004531833</v>
+        <v>42.39126811181405</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.69442007796341</v>
+        <v>17.79510086497888</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4320424584521025</v>
+        <v>0.7157423507806016</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.9709125227310796</v>
+        <v>-8.947872376930704</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6807</v>
+        <v>6585</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>329.4960519282362</v>
+        <v>333.2175191820899</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>32.6</v>
+        <v>102.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.23821463411581</v>
+        <v>31.34088004531833</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.77042407018704</v>
+        <v>27.69442007796341</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2101027927913732</v>
+        <v>0.4320424584521025</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1963208638946008</v>
+        <v>-0.9709125227310796</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6488</v>
+        <v>6807</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>327.4447246075782</v>
+        <v>329.4960519282362</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>914</v>
+        <v>32.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.91704779329347</v>
+        <v>50.23821463411581</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8.077433922447812</v>
+        <v>21.77042407018704</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.858045705057465</v>
+        <v>0.2101027927913732</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-3.597654332586803</v>
+        <v>-0.1963208638946008</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6570</v>
+        <v>6488</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>322.5979181018179</v>
+        <v>327.4447246075782</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46.2</v>
+        <v>914</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>29.24644010955909</v>
+        <v>44.91704779329347</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.73820759149592</v>
+        <v>8.077433922447812</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.468589147934307</v>
+        <v>0.858045705057465</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>1</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.5723525705754406</v>
+        <v>-3.597654332586803</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6526</v>
+        <v>6570</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>321.5971753392107</v>
+        <v>322.5979181018179</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>623</v>
+        <v>46.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.81828645672075</v>
+        <v>29.24644010955909</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.87777562361441</v>
+        <v>23.73820759149592</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4074006682966389</v>
+        <v>1.468589147934307</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1696859250311124</v>
+        <v>-0.5723525705754406</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6674</v>
+        <v>6526</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>318.477080973477</v>
+        <v>321.5971753392107</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>15.6</v>
+        <v>623</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.34754057264069</v>
+        <v>50.81828645672075</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.25070067388697</v>
+        <v>15.87777562361441</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.0626224562562573</v>
+        <v>0.4074006682966389</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0167934259617931</v>
+        <v>-0.1696859250311124</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6698</v>
+        <v>6674</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>317.0513360069775</v>
+        <v>318.477080973477</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31.45</v>
+        <v>15.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.45891442163721</v>
+        <v>45.34754057264069</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.44458287281956</v>
+        <v>24.25070067388697</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.067114582076314</v>
+        <v>0.0626224562562573</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0948601679065752</v>
+        <v>-0.0167934259617931</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6494</v>
+        <v>6698</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>312.7593026810555</v>
+        <v>317.0513360069775</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>49.05</v>
+        <v>31.45</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.62993182386408</v>
+        <v>44.45891442163721</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.50402741119223</v>
+        <v>14.44458287281956</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4278716488406388</v>
+        <v>1.067114582076314</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.6315998092626143</v>
+        <v>0.0948601679065752</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6720</v>
+        <v>6494</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>312.1602288933635</v>
+        <v>312.7593026810555</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>129.5</v>
+        <v>49.05</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.86645392230384</v>
+        <v>32.62993182386408</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>31.16962654337643</v>
+        <v>14.50402741119223</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3152616671837625</v>
+        <v>0.4278716488406388</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.426050203455352</v>
+        <v>-0.6315998092626143</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6598</v>
+        <v>6720</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>312.1082693297781</v>
+        <v>312.1602288933635</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>27.15</v>
+        <v>129.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.67836457543596</v>
+        <v>50.86645392230384</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.99061999056006</v>
+        <v>31.16962654337643</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5616602187380784</v>
+        <v>0.3152616671837625</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0843757744809306</v>
+        <v>-2.426050203455352</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6568</v>
+        <v>6598</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>308.9545321480472</v>
+        <v>312.1082693297781</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>131.5</v>
+        <v>27.15</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.56066417094555</v>
+        <v>44.67836457543596</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.73873266098996</v>
+        <v>17.99061999056006</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.45085823896095</v>
+        <v>0.5616602187380784</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.6383728568742741</v>
+        <v>-0.0843757744809306</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6533</v>
+        <v>6568</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>307.3673535675881</v>
+        <v>308.9545321480472</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>224.5</v>
+        <v>131.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.39936740100798</v>
+        <v>45.56066417094555</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.20098024902394</v>
+        <v>21.73873266098996</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.440287414997807</v>
+        <v>0.45085823896095</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-5.378831090226885</v>
+        <v>0.6383728568742741</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6680</v>
+        <v>6533</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>303.0846320284457</v>
+        <v>307.3673535675881</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>53.8</v>
+        <v>224.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.30382858440165</v>
+        <v>33.39936740100798</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7.224625691660367</v>
+        <v>18.20098024902394</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3192279138827023</v>
+        <v>0.440287414997807</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>2.073186268348497</v>
+        <v>-5.378831090226885</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6531</v>
+        <v>6680</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>302.4365568750589</v>
+        <v>303.0846320284457</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>890</v>
+        <v>53.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.97836039679627</v>
+        <v>52.30382858440165</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.56313232508917</v>
+        <v>7.224625691660367</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.050684230849987</v>
+        <v>0.3192279138827023</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.9694251571565538</v>
+        <v>2.073186268348497</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6643</v>
+        <v>6531</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>299.3057765231019</v>
+        <v>302.4365568750589</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>410</v>
+        <v>890</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.91520497169098</v>
+        <v>46.97836039679627</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.19606754718309</v>
+        <v>13.56313232508917</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5679584116835216</v>
+        <v>1.050684230849987</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.099972886997548</v>
+        <v>-0.9694251571565538</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6753</v>
+        <v>6643</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>297.5285864122444</v>
+        <v>299.3057765231019</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.01886552583005</v>
+        <v>45.91520497169098</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.8842410702118</v>
+        <v>11.19606754718309</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3519624676361229</v>
+        <v>0.5679584116835216</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.067941029578465</v>
+        <v>0.099972886997548</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6517</v>
+        <v>6753</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>294.2314136577339</v>
+        <v>297.5285864122444</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>39.28136872809146</v>
+        <v>38.01886552583005</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.95424725723462</v>
+        <v>15.8842410702118</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2191008692307227</v>
+        <v>0.3519624676361229</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.9114630498923511</v>
+        <v>-1.067941029578465</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6525</v>
+        <v>6517</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>293.9740414006301</v>
+        <v>294.2314136577339</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>125.5</v>
+        <v>61</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.33604474562237</v>
+        <v>39.28136872809146</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.1403241569014</v>
+        <v>14.95424725723462</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4161790805666895</v>
+        <v>0.2191008692307227</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.071971401175412</v>
+        <v>-0.9114630498923511</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6761</v>
+        <v>6525</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>292.1109195631549</v>
+        <v>293.9740414006301</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>160</v>
+        <v>125.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.06991224186371</v>
+        <v>38.33604474562237</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.61810832116402</v>
+        <v>14.1403241569014</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.263515432253164</v>
+        <v>0.4161790805666895</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-3.410868175146517</v>
+        <v>-1.071971401175412</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6831</v>
+        <v>6761</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>290.2090546493695</v>
+        <v>292.1109195631549</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>513</v>
+        <v>160</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>36.51483455846478</v>
+        <v>36.06991224186371</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.36913089716208</v>
+        <v>19.61810832116402</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5222931561315747</v>
+        <v>0.263515432253164</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-4.867495788659401</v>
+        <v>-3.410868175146517</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6558</v>
+        <v>6831</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>282.8072968949785</v>
+        <v>290.2090546493695</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>23.05</v>
+        <v>513</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>34.7542776367863</v>
+        <v>36.51483455846478</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>30.23351631774336</v>
+        <v>15.36913089716208</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.164632224135858</v>
+        <v>0.5222931561315747</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0710958203926931</v>
+        <v>-4.867495788659401</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6803</v>
+        <v>6558</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>273.3904506141408</v>
+        <v>282.8072968949785</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>269</v>
+        <v>23.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.90748660037212</v>
+        <v>34.7542776367863</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.2421965735205</v>
+        <v>30.23351631774336</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8908913081819494</v>
+        <v>1.164632224135858</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0303414327948645</v>
+        <v>-0.0710958203926931</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6739</v>
+        <v>6803</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>270.4670163630261</v>
+        <v>273.3904506141408</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1065</v>
+        <v>269</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.95525871023477</v>
+        <v>44.90748660037212</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.40256311489622</v>
+        <v>14.2421965735205</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9467016363026119</v>
+        <v>0.8908913081819494</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>3.131075020926985</v>
+        <v>0.0303414327948645</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6741</v>
+        <v>6739</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>269.4921520298414</v>
+        <v>270.4670163630261</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>58.8</v>
+        <v>1065</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.53889947047806</v>
+        <v>46.95525871023477</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.08208606618707</v>
+        <v>15.40256311489622</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3148639008945479</v>
+        <v>0.9467016363026119</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0741836119600604</v>
+        <v>3.131075020926985</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6541</v>
+        <v>6741</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>257.7121714541843</v>
+        <v>269.4921520298414</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>30.3</v>
+        <v>58.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>24.20871514809545</v>
+        <v>52.53889947047806</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>32.7750701998858</v>
+        <v>25.08208606618707</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7802169287456536</v>
+        <v>0.3148639008945479</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1874285071794579</v>
+        <v>-0.0741836119600604</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6645</v>
+        <v>6541</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>256.9876992694549</v>
+        <v>257.7121714541843</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>12.65</v>
+        <v>30.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.2106064640281</v>
+        <v>24.20871514809545</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>28.74257924226444</v>
+        <v>32.7750701998858</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.406692767434921</v>
+        <v>0.7802169287456536</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0875295788035661</v>
+        <v>-0.1874285071794579</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6776</v>
+        <v>6645</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>256.2050271940897</v>
+        <v>256.9876992694549</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>51.7</v>
+        <v>12.65</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>34.12480457737168</v>
+        <v>46.2106064640281</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.20380124031722</v>
+        <v>28.74257924226444</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6001828888828895</v>
+        <v>1.406692767434921</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1038338134294357</v>
+        <v>0.0875295788035661</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6512</v>
+        <v>6776</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>254.8438978993679</v>
+        <v>256.2050271940897</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>20.35</v>
+        <v>51.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.58250006949528</v>
+        <v>34.12480457737168</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.391652823698729</v>
+        <v>20.20380124031722</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.398331900745261</v>
+        <v>0.6001828888828895</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4400568033047703</v>
+        <v>-0.1038338134294357</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6561</v>
+        <v>6512</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>246.9528096356314</v>
+        <v>254.8438978993679</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>308</v>
+        <v>20.35</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>28.78918338132056</v>
+        <v>52.58250006949528</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.33921079930718</v>
+        <v>8.391652823698729</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.591575173650011</v>
+        <v>1.398331900745261</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.05413059583562</v>
+        <v>0.4400568033047703</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6796</v>
+        <v>6561</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>240.2672200445179</v>
+        <v>246.9528096356314</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>50.9</v>
+        <v>308</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>27.61977454343044</v>
+        <v>28.78918338132056</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.49088849168069</v>
+        <v>11.33921079930718</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4267220044517874</v>
+        <v>2.591575173650011</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.187560976133675</v>
+        <v>-1.05413059583562</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6582</v>
+        <v>6796</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>239.2182165024866</v>
+        <v>240.2672200445179</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>31.2</v>
+        <v>50.9</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>37.06151480400904</v>
+        <v>27.61977454343044</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.78392025408453</v>
+        <v>24.49088849168069</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6375609879414517</v>
+        <v>0.4267220044517874</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1100130124518588</v>
+        <v>-1.187560976133675</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6550</v>
+        <v>6582</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>237.7513331898772</v>
+        <v>239.2182165024866</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>9.9</v>
+        <v>31.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>35.48141256780097</v>
+        <v>37.06151480400904</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.03797678471005</v>
+        <v>22.78392025408453</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5883929472429978</v>
+        <v>0.6375609879414517</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0420956673867823</v>
+        <v>-0.1100130124518588</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6756</v>
+        <v>6550</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>236.36722144494</v>
+        <v>237.7513331898772</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>93.8</v>
+        <v>9.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.40046972400107</v>
+        <v>35.48141256780097</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11.16526087181605</v>
+        <v>15.03797678471005</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5696220441873784</v>
+        <v>0.5883929472429978</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.8874812861748513</v>
+        <v>-0.0420956673867823</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6788</v>
+        <v>6756</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>233.2818143033349</v>
+        <v>236.36722144494</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>318.5</v>
+        <v>93.8</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>33.17673533822591</v>
+        <v>39.40046972400107</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.49043398057506</v>
+        <v>11.16526087181605</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.510255585512131</v>
+        <v>0.5696220441873784</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-4.08889859630206</v>
+        <v>-0.8874812861748513</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6504</v>
+        <v>6788</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>232.40594608593</v>
+        <v>233.2818143033349</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>36.55</v>
+        <v>318.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.37958583523655</v>
+        <v>33.17673533822591</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.23011650665331</v>
+        <v>17.49043398057506</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9270785438543978</v>
+        <v>0.510255585512131</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0968042149228681</v>
+        <v>-4.08889859630206</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6606</v>
+        <v>6504</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>229.9363553739541</v>
+        <v>232.40594608593</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.05</v>
+        <v>36.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.87972827004635</v>
+        <v>41.37958583523655</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.15823514512638</v>
+        <v>18.23011650665331</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.977034281645448</v>
+        <v>0.9270785438543978</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0640555865229961</v>
+        <v>-0.0968042149228681</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6781</v>
+        <v>6606</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>228.8312311730262</v>
+        <v>229.9363553739541</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>982</v>
+        <v>25.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.66708049160312</v>
+        <v>38.87972827004635</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.15266471453275</v>
+        <v>13.15823514512638</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6153892006981713</v>
+        <v>0.977034281645448</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-14.1589308462475</v>
+        <v>-0.0640555865229961</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6725</v>
+        <v>6781</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>227.3201608636593</v>
+        <v>228.8312311730262</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>207</v>
+        <v>982</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>33.08233052375421</v>
+        <v>38.66708049160312</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>32.29566351236539</v>
+        <v>12.15266471453275</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5096293863323172</v>
+        <v>0.6153892006981713</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1769389967374763</v>
+        <v>-14.1589308462475</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6792</v>
+        <v>6725</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>223.7885136935359</v>
+        <v>227.3201608636593</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>58.7</v>
+        <v>207</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.42134227823785</v>
+        <v>33.08233052375421</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.99602467821163</v>
+        <v>32.29566351236539</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8455448650196725</v>
+        <v>0.5096293863323172</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1499114235905514</v>
+        <v>0.1769389967374763</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6573</v>
+        <v>6792</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>222.0853596890948</v>
+        <v>223.7885136935359</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15.55</v>
+        <v>58.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.73663528224866</v>
+        <v>49.42134227823785</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.944256527493</v>
+        <v>15.99602467821163</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2762074003332637</v>
+        <v>0.8455448650196725</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0870065118137303</v>
+        <v>-0.1499114235905514</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6835</v>
+        <v>6573</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>215.2602299392173</v>
+        <v>222.0853596890948</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>30.35</v>
+        <v>15.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.23913064788284</v>
+        <v>38.73663528224866</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.13293298475347</v>
+        <v>15.944256527493</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8165598334217939</v>
+        <v>0.2762074003332637</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0307494704935633</v>
+        <v>-0.0870065118137303</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6477</v>
+        <v>6835</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>213.5201847195975</v>
+        <v>215.2602299392173</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>33.5</v>
+        <v>30.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.77145410013408</v>
+        <v>38.23913064788284</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.0801755594345</v>
+        <v>16.13293298475347</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2112500061323897</v>
+        <v>0.8165598334217939</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2394019317084486</v>
+        <v>-0.0307494704935633</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6692</v>
+        <v>6477</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>212.7587850864012</v>
+        <v>213.5201847195975</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>11.6381693738148</v>
+        <v>39.77145410013408</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.4962526721524</v>
+        <v>12.0801755594345</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.0004244947627958</v>
+        <v>0.2112500061323897</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.532880292492481</v>
+        <v>-0.2394019317084486</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6763</v>
+        <v>6692</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>212.1653529518777</v>
+        <v>212.7587850864012</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.45642302589403</v>
+        <v>11.6381693738148</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.44973859149418</v>
+        <v>12.4962526721524</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5154748586828494</v>
+        <v>0.0004244947627958</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0202873050420996</v>
+        <v>-1.532880292492481</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6597</v>
+        <v>6763</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>209.7679815508827</v>
+        <v>212.1653529518777</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.49741881350598</v>
+        <v>41.45642302589403</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7.826441305977135</v>
+        <v>17.44973859149418</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0</v>
+        <v>0.5154748586828494</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-6.202214389039652</v>
+        <v>0.0202873050420996</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6794</v>
+        <v>6597</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>208.0808578875006</v>
+        <v>209.7679815508827</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>76.5</v>
+        <v>0</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>53.61595159393431</v>
+        <v>44.49741881350598</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.85877120375163</v>
+        <v>7.826441305977135</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5514588672000882</v>
+        <v>0</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2139358424321801</v>
+        <v>-6.202214389039652</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6754</v>
+        <v>6794</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>204.688847106365</v>
+        <v>208.0808578875006</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>41.3</v>
+        <v>76.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.3615823867642</v>
+        <v>53.61595159393431</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.83075256293734</v>
+        <v>14.85877120375163</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.35529736456267</v>
+        <v>0.5514588672000882</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0262342218962327</v>
+        <v>0.2139358424321801</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6679</v>
+        <v>6754</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>202.0219620263189</v>
+        <v>204.688847106365</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>194</v>
+        <v>41.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.49132655446332</v>
+        <v>40.3615823867642</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.74782722179636</v>
+        <v>11.83075256293734</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4529294425319563</v>
+        <v>1.35529736456267</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1308037316456909</v>
+        <v>-0.0262342218962327</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6591</v>
+        <v>6679</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>201.9091007234731</v>
+        <v>202.0219620263189</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>41.5</v>
+        <v>194</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>34.04562650924261</v>
+        <v>38.49132655446332</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27.52570390764999</v>
+        <v>15.74782722179636</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2803082178939213</v>
+        <v>0.4529294425319563</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.053820707827655</v>
+        <v>0.1308037316456909</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6695</v>
+        <v>6591</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>199.3187662280061</v>
+        <v>201.9091007234731</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>45.6</v>
+        <v>41.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.80260550998195</v>
+        <v>34.04562650924261</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.45501760667881</v>
+        <v>27.52570390764999</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6231875811082487</v>
+        <v>0.2803082178939213</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1619918119958316</v>
+        <v>0.053820707827655</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6732</v>
+        <v>6695</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>198.331420814764</v>
+        <v>199.3187662280061</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>145</v>
+        <v>45.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.28771697544619</v>
+        <v>37.80260550998195</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.20683711521637</v>
+        <v>10.45501760667881</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4379044903039937</v>
+        <v>0.6231875811082487</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1143377587690555</v>
+        <v>-0.1619918119958316</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6625</v>
+        <v>6732</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>192.6740472913893</v>
+        <v>198.331420814764</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>73.3</v>
+        <v>145</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>31.60073219490154</v>
+        <v>35.28771697544619</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.90247580980472</v>
+        <v>21.20683711521637</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.108250127880636</v>
+        <v>0.4379044903039937</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3566440240004513</v>
+        <v>0.1143377587690555</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6641</v>
+        <v>6625</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>187.1691036363342</v>
+        <v>192.6740472913893</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16.8</v>
+        <v>73.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.80090199795862</v>
+        <v>31.60073219490154</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.14104600130454</v>
+        <v>12.90247580980472</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5408985539242742</v>
+        <v>1.108250127880636</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.6716421589748294</v>
+        <v>-0.3566440240004513</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6757</v>
+        <v>6641</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>180.7299104772259</v>
+        <v>187.1691036363342</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>52.8</v>
+        <v>16.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>32.82407164243739</v>
+        <v>50.80090199795862</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.82193767433654</v>
+        <v>13.14104600130454</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.147382013006891</v>
+        <v>0.5408985539242742</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.234484837867129</v>
+        <v>-0.6716421589748294</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6823</v>
+        <v>6757</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>179.9783234544442</v>
+        <v>180.7299104772259</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.03488932398329</v>
+        <v>32.82407164243739</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>26.58840304872127</v>
+        <v>14.82193767433654</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.589992274084939</v>
+        <v>1.147382013006891</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1638561239075391</v>
+        <v>-0.234484837867129</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6577</v>
+        <v>6823</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>179.7189408630273</v>
+        <v>179.9783234544442</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,49 +6329,49 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.23321473076297</v>
+        <v>32.03488932398329</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.39478162477899</v>
+        <v>26.58840304872127</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4664613563658833</v>
+        <v>0.589992274084939</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1730803734393382</v>
+        <v>-0.1638561239075391</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6485</v>
+        <v>6577</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>176.8982323595753</v>
+        <v>179.7189408630273</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>58.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.66297459715134</v>
+        <v>48.23321473076297</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.65434701930349</v>
+        <v>13.39478162477899</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6226546632266564</v>
+        <v>0.4664613563658833</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0750868384110949</v>
+        <v>-0.1730803734393382</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6614</v>
+        <v>6485</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>175.8853076144632</v>
+        <v>176.8982323595753</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.45</v>
+        <v>58.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.51332355974097</v>
+        <v>39.66297459715134</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.921131829372891</v>
+        <v>17.65434701930349</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8269730931101338</v>
+        <v>0.6226546632266564</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0696375454275921</v>
+        <v>0.0750868384110949</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6735</v>
+        <v>6614</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>175.2459504453126</v>
+        <v>175.8853076144632</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>59.5</v>
+        <v>35.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.79363744208981</v>
+        <v>38.51332355974097</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.49100482284694</v>
+        <v>8.921131829372891</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3582425175824369</v>
+        <v>0.8269730931101338</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0213180747461272</v>
+        <v>0.0696375454275921</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6546</v>
+        <v>6735</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>175.056979942896</v>
+        <v>175.2459504453126</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>59.1</v>
+        <v>59.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.19894720840098</v>
+        <v>37.79363744208981</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.14629030657742</v>
+        <v>15.49100482284694</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6557294252318304</v>
+        <v>0.3582425175824369</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3996456295917787</v>
+        <v>-0.0213180747461272</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6799</v>
+        <v>6546</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>159.209426999745</v>
+        <v>175.056979942896</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>77.5</v>
+        <v>59.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.00999686685219</v>
+        <v>38.19894720840098</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.45947144369166</v>
+        <v>15.14629030657742</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5852070196633776</v>
+        <v>0.6557294252318304</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0114678538481445</v>
+        <v>-0.3996456295917787</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6556</v>
+        <v>6799</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>156.8852291745426</v>
+        <v>159.209426999745</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>60.4</v>
+        <v>77.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.2532961407496</v>
+        <v>40.00999686685219</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.99318322059976</v>
+        <v>11.45947144369166</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.047055300918995</v>
+        <v>0.5852070196633776</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2016415978826617</v>
+        <v>-0.0114678538481445</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6722</v>
+        <v>6556</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>156.6811076881782</v>
+        <v>156.8852291745426</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>32</v>
+        <v>60.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>38.06439528466851</v>
+        <v>42.2532961407496</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.60424064399069</v>
+        <v>10.99318322059976</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5188943268217573</v>
+        <v>1.047055300918995</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0089126671795812</v>
+        <v>0.2016415978826617</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6790</v>
+        <v>6722</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>142.326835495661</v>
+        <v>156.6811076881782</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>37.7</v>
+        <v>32</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>36.33630539151475</v>
+        <v>38.06439528466851</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.05790477359376</v>
+        <v>18.60424064399069</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4220671035431422</v>
+        <v>0.5188943268217573</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0015788055796502</v>
+        <v>-0.0089126671795812</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6624</v>
+        <v>6790</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>139.5361831699181</v>
+        <v>142.326835495661</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>39.3</v>
+        <v>37.7</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.29092474145263</v>
+        <v>36.33630539151475</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>7.808072730610379</v>
+        <v>11.05790477359376</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.456411217839144</v>
+        <v>0.4220671035431422</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.9064978697798416</v>
+        <v>0.0015788055796502</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6589</v>
+        <v>6624</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>122.5497348494258</v>
+        <v>139.5361831699181</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>48.65</v>
+        <v>39.3</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>51.18139449671824</v>
+        <v>52.29092474145263</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.11309897118648</v>
+        <v>7.808072730610379</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.116509743798567</v>
+        <v>2.456411217839144</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.169087938837338</v>
+        <v>0.9064978697798416</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6592</v>
+        <v>6589</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>117.1676563879708</v>
+        <v>122.5497348494258</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>59.7</v>
+        <v>48.65</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.82780625409865</v>
+        <v>51.18139449671824</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.129104843936188</v>
+        <v>15.11309897118648</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4044827886728322</v>
+        <v>1.116509743798567</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1287719961965023</v>
+        <v>-0.169087938837338</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6534</v>
+        <v>6592</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>116.5328321478974</v>
+        <v>117.1676563879708</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>89.8</v>
+        <v>59.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>35.85104827792379</v>
+        <v>40.82780625409865</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.56288165637492</v>
+        <v>9.129104843936188</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6345408467501491</v>
+        <v>0.4044827886728322</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.14934183942238</v>
+        <v>-0.1287719961965023</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6498</v>
+        <v>6534</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>99.75925945924138</v>
+        <v>116.5328321478974</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>64.2</v>
+        <v>89.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>33.03410556992419</v>
+        <v>35.85104827792379</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.14030664097076</v>
+        <v>11.56288165637492</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.6387701756265498</v>
+        <v>0.6345408467501491</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.8569911681835185</v>
+        <v>-0.14934183942238</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6821</v>
+        <v>6498</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>92.94289006121544</v>
+        <v>99.75925945924138</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>40.1</v>
+        <v>64.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>41.36950589923519</v>
+        <v>33.03410556992419</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.22418726682034</v>
+        <v>18.14030664097076</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3058378731118277</v>
+        <v>0.6387701756265498</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0447471759951405</v>
+        <v>-0.8569911681835185</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6552</v>
+        <v>6821</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>81.924143193004</v>
+        <v>92.94289006121544</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>23.35</v>
+        <v>40.1</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>32.18698571043684</v>
+        <v>41.36950589923519</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.05024117334909</v>
+        <v>13.22418726682034</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4003261863807118</v>
+        <v>0.3058378731118277</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0725395931883262</v>
+        <v>0.0447471759951405</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>易華電</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>81.924143193004</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>32.18698571043684</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>17.05024117334909</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4003261863807118</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0725395931883262</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6671</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>三能-KY</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>75.21845035870281</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>22.75</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>43.94320100494959</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>13.41992799479794</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.0964326006184264</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-0.0038447623886679</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
